--- a/docs/plantillas/importar-compras-ejemplo.xlsx
+++ b/docs/plantillas/importar-compras-ejemplo.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,500 +397,491 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y6"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="25.83203125" customWidth="1"/>
-    <col min="20" max="20" width="19.83203125" customWidth="1"/>
-    <col min="21" max="21" width="12.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="16.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:Z6"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
+      <c r="A1" t="str">
         <v>TIPO DE COMPRA</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" t="str">
         <v>LÍNEA DE NEGOCIO</v>
       </c>
-      <c r="C1" s="1" t="str">
+      <c r="C1" t="str">
         <v>TIPO DE COMPROBANTE</v>
       </c>
-      <c r="D1" s="1" t="str">
+      <c r="D1" t="str">
         <v>SERIE-NÚMERO</v>
       </c>
-      <c r="E1" s="1" t="str">
+      <c r="E1" t="str">
         <v>FECHA DE EMISIÓN</v>
       </c>
-      <c r="F1" s="1" t="str">
+      <c r="F1" t="str">
         <v>RUC PROVEEDOR</v>
       </c>
-      <c r="G1" s="1" t="str">
+      <c r="G1" t="str">
         <v>MONEDA</v>
       </c>
-      <c r="H1" s="1" t="str">
+      <c r="H1" t="str">
         <v>TIPO DE CAMBIO</v>
       </c>
-      <c r="I1" s="1" t="str">
+      <c r="I1" t="str">
         <v>CONDICIÓN DE PAGO</v>
       </c>
-      <c r="J1" s="1" t="str">
+      <c r="J1" t="str">
         <v>DÍAS DE CRÉDITO</v>
       </c>
-      <c r="K1" s="1" t="str">
+      <c r="K1" t="str">
         <v>TIPO DE SERVICIO</v>
       </c>
-      <c r="L1" s="1" t="str">
+      <c r="L1" t="str">
         <v>TASA IGV</v>
       </c>
-      <c r="M1" s="1" t="str">
+      <c r="M1" t="str">
         <v>OBSERVACIONES</v>
       </c>
-      <c r="N1" s="1" t="str">
-        <v>TOTAL COMPROBANTE</v>
-      </c>
-      <c r="O1" s="1" t="str">
+      <c r="N1" t="str">
+        <v>TOTAL COMPROBANTE CON IGV</v>
+      </c>
+      <c r="O1" t="str">
         <v>SKU</v>
       </c>
-      <c r="P1" s="1" t="str">
+      <c r="P1" t="str">
         <v>DESCRIPCIÓN</v>
       </c>
-      <c r="Q1" s="1" t="str">
+      <c r="Q1" t="str">
         <v>CANTIDAD</v>
       </c>
-      <c r="R1" s="1" t="str">
+      <c r="R1" t="str">
         <v>UNIDAD</v>
       </c>
-      <c r="S1" s="1" t="str">
+      <c r="S1" t="str">
         <v>PRECIO UNITARIO SIN IGV</v>
       </c>
-      <c r="T1" s="1" t="str">
+      <c r="T1" t="str">
+        <v>IMPORTE SIN IGV</v>
+      </c>
+      <c r="U1" t="str">
         <v>CÓDIGO DE ACABADO</v>
       </c>
-      <c r="U1" s="1" t="str">
+      <c r="V1" t="str">
         <v>COLOR</v>
       </c>
-      <c r="V1" s="1" t="str">
+      <c r="W1" t="str">
         <v>ESPESOR MM</v>
       </c>
-      <c r="W1" s="1" t="str">
+      <c r="X1" t="str">
         <v>ANCHO MM</v>
       </c>
-      <c r="X1" s="1" t="str">
+      <c r="Y1" t="str">
         <v>KG</v>
       </c>
-      <c r="Y1" s="1" t="str">
+      <c r="Z1" t="str">
         <v>CÓDIGO EXTERNO</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="str">
+      <c r="A2" t="str">
         <v>Bobinas</v>
       </c>
-      <c r="B2" s="1" t="str">
+      <c r="B2" t="str">
         <v>Coberturas Aluzinc</v>
       </c>
-      <c r="C2" s="1" t="str">
+      <c r="C2" t="str">
         <v>Factura</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" t="str">
         <v>F001-00004567</v>
       </c>
-      <c r="E2" s="1" t="str">
+      <c r="E2" t="str">
         <v>15/09/2026</v>
       </c>
-      <c r="F2" s="1" t="str">
+      <c r="F2" t="str">
         <v>20100000001</v>
       </c>
-      <c r="G2" s="1" t="str">
+      <c r="G2" t="str">
         <v>USD</v>
       </c>
-      <c r="H2" s="1" t="str">
+      <c r="H2" t="str">
         <v>3,745</v>
       </c>
-      <c r="I2" s="1" t="str">
+      <c r="I2" t="str">
         <v>Crédito</v>
       </c>
-      <c r="J2" s="1" t="str">
+      <c r="J2" t="str">
         <v>30</v>
       </c>
-      <c r="K2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L2" s="1" t="str">
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>18</v>
       </c>
-      <c r="M2" s="1" t="str">
+      <c r="M2" t="str">
         <v>Importación setiembre</v>
       </c>
-      <c r="N2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="P2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="Q2" s="1" t="str">
-        <v/>
-      </c>
-      <c r="R2" s="1" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
         <v>KGM</v>
       </c>
-      <c r="S2" s="1" t="str">
+      <c r="S2" t="str">
         <v>0,98</v>
       </c>
-      <c r="T2" s="1" t="str">
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
         <v>ALZ-ROJO-3002</v>
       </c>
-      <c r="U2" s="1" t="str">
+      <c r="V2" t="str">
         <v>Rojo</v>
       </c>
-      <c r="V2" s="1" t="str">
+      <c r="W2" t="str">
         <v>0,30</v>
       </c>
-      <c r="W2" s="1" t="str">
+      <c r="X2" t="str">
         <v>1220</v>
       </c>
-      <c r="X2" s="1" t="str">
+      <c r="Y2" t="str">
         <v>4520,5</v>
       </c>
-      <c r="Y2" s="1" t="str">
+      <c r="Z2" t="str">
         <v>PR-88121</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="str">
+      <c r="A3" t="str">
         <v>Bobinas</v>
       </c>
-      <c r="B3" s="1" t="str">
+      <c r="B3" t="str">
         <v>Coberturas Aluzinc</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C3" t="str">
         <v>Factura</v>
       </c>
-      <c r="D3" s="1" t="str">
+      <c r="D3" t="str">
         <v>F001-00004567</v>
       </c>
-      <c r="E3" s="1" t="str">
+      <c r="E3" t="str">
         <v>15/09/2026</v>
       </c>
-      <c r="F3" s="1" t="str">
+      <c r="F3" t="str">
         <v>20100000001</v>
       </c>
-      <c r="G3" s="1" t="str">
+      <c r="G3" t="str">
         <v>USD</v>
       </c>
-      <c r="H3" s="1" t="str">
+      <c r="H3" t="str">
         <v>3,745</v>
       </c>
-      <c r="I3" s="1" t="str">
+      <c r="I3" t="str">
         <v>Crédito</v>
       </c>
-      <c r="J3" s="1" t="str">
+      <c r="J3" t="str">
         <v>30</v>
       </c>
-      <c r="K3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L3" s="1" t="str">
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>18</v>
       </c>
-      <c r="M3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="N3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="P3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="Q3" s="1" t="str">
-        <v/>
-      </c>
-      <c r="R3" s="1" t="str">
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
         <v>KGM</v>
       </c>
-      <c r="S3" s="1" t="str">
+      <c r="S3" t="str">
         <v>0,98</v>
       </c>
-      <c r="T3" s="1" t="str">
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
         <v>ALZ-ROJO-3002</v>
       </c>
-      <c r="U3" s="1" t="str">
+      <c r="V3" t="str">
         <v>Rojo</v>
       </c>
-      <c r="V3" s="1" t="str">
+      <c r="W3" t="str">
         <v>0,30</v>
       </c>
-      <c r="W3" s="1" t="str">
+      <c r="X3" t="str">
         <v>1220</v>
       </c>
-      <c r="X3" s="1" t="str">
+      <c r="Y3" t="str">
         <v>4310</v>
       </c>
-      <c r="Y3" s="1" t="str">
+      <c r="Z3" t="str">
         <v>PR-88122</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="str">
+      <c r="A4" t="str">
         <v>Producto terminado</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B4" t="str">
         <v>Reventa</v>
       </c>
-      <c r="C4" s="1" t="str">
+      <c r="C4" t="str">
         <v>Factura</v>
       </c>
-      <c r="D4" s="1" t="str">
+      <c r="D4" t="str">
         <v>F002-00000891</v>
       </c>
-      <c r="E4" s="1" t="str">
+      <c r="E4" t="str">
         <v>18/09/2026</v>
       </c>
-      <c r="F4" s="1" t="str">
+      <c r="F4" t="str">
         <v>20200000002</v>
       </c>
-      <c r="G4" s="1" t="str">
+      <c r="G4" t="str">
         <v>PEN</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I4" s="1" t="str">
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>Contado</v>
       </c>
-      <c r="J4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L4" s="1" t="str">
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>18</v>
       </c>
-      <c r="M4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="N4" s="1" t="str">
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>1180,00</v>
       </c>
-      <c r="O4" s="1" t="str">
+      <c r="O4" t="str">
         <v>CLAVO-1</v>
       </c>
-      <c r="P4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="Q4" s="1" t="str">
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
         <v>500</v>
       </c>
-      <c r="R4" s="1" t="str">
+      <c r="R4" t="str">
         <v>NIU</v>
       </c>
-      <c r="S4" s="1" t="str">
+      <c r="S4" t="str">
         <v>2,00</v>
       </c>
-      <c r="T4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="U4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="V4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="W4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="X4" s="1" t="str">
-        <v/>
-      </c>
-      <c r="Y4" s="1" t="str">
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="str">
+      <c r="A5" t="str">
         <v>Servicio</v>
       </c>
-      <c r="B5" s="1" t="str">
+      <c r="B5" t="str">
         <v>Coberturas Aluzinc</v>
       </c>
-      <c r="C5" s="1" t="str">
+      <c r="C5" t="str">
         <v>Factura</v>
       </c>
-      <c r="D5" s="1" t="str">
+      <c r="D5" t="str">
         <v>E001-000123</v>
       </c>
-      <c r="E5" s="1" t="str">
+      <c r="E5" t="str">
         <v>16/09/2026</v>
       </c>
-      <c r="F5" s="1" t="str">
+      <c r="F5" t="str">
         <v>20300000003</v>
       </c>
-      <c r="G5" s="1" t="str">
+      <c r="G5" t="str">
         <v>PEN</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I5" s="1" t="str">
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>Contado</v>
       </c>
-      <c r="J5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K5" s="1" t="str">
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>Flete</v>
       </c>
-      <c r="L5" s="1" t="str">
+      <c r="L5" t="str">
         <v>18</v>
       </c>
-      <c r="M5" s="1" t="str">
+      <c r="M5" t="str">
         <v>Flete Callao - planta</v>
       </c>
-      <c r="N5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="P5" s="1" t="str">
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
         <v>Flete de bobinas F001-4567</v>
       </c>
-      <c r="Q5" s="1" t="str">
+      <c r="Q5" t="str">
         <v>1</v>
       </c>
-      <c r="R5" s="1" t="str">
+      <c r="R5" t="str">
         <v>ZZ</v>
       </c>
-      <c r="S5" s="1" t="str">
+      <c r="S5" t="str">
         <v>850</v>
       </c>
-      <c r="T5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="U5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="V5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="W5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="X5" s="1" t="str">
-        <v/>
-      </c>
-      <c r="Y5" s="1" t="str">
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="str">
+      <c r="A6" t="str">
         <v>Gasto</v>
       </c>
-      <c r="B6" s="1" t="str">
+      <c r="B6" t="str">
         <v>Servicios</v>
       </c>
-      <c r="C6" s="1" t="str">
+      <c r="C6" t="str">
         <v>Boleta</v>
       </c>
-      <c r="D6" s="1" t="str">
+      <c r="D6" t="str">
         <v>B001-00045678</v>
       </c>
-      <c r="E6" s="1" t="str">
+      <c r="E6" t="str">
         <v>20/09/2026</v>
       </c>
-      <c r="F6" s="1" t="str">
+      <c r="F6" t="str">
         <v>20400000004</v>
       </c>
-      <c r="G6" s="1" t="str">
+      <c r="G6" t="str">
         <v>PEN</v>
       </c>
-      <c r="H6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="I6" s="1" t="str">
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>Contado</v>
       </c>
-      <c r="J6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="K6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="L6" s="1" t="str">
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>18</v>
       </c>
-      <c r="M6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="N6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="O6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="P6" s="1" t="str">
+      <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
         <v>Energía eléctrica setiembre</v>
       </c>
-      <c r="Q6" s="1" t="str">
+      <c r="Q6" t="str">
         <v>1</v>
       </c>
-      <c r="R6" s="1" t="str">
+      <c r="R6" t="str">
         <v>NIU</v>
       </c>
-      <c r="S6" s="1" t="str">
+      <c r="S6" t="str">
         <v>420,50</v>
       </c>
-      <c r="T6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="U6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="V6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="W6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="X6" s="1" t="str">
-        <v/>
-      </c>
-      <c r="Y6" s="1" t="str">
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6" t="str">
+        <v/>
+      </c>
+      <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
+        <v/>
+      </c>
+      <c r="Z6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z6"/>
   </ignoredErrors>
 </worksheet>
 </file>